--- a/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
+++ b/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
@@ -48,7 +54,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +64,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -98,11 +109,55 @@
         <color rgb="00B8CCE4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -111,13 +166,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,14 +551,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
     <col width="69" customWidth="1" min="2" max="2"/>
     <col width="69" customWidth="1" min="3" max="3"/>
-    <col width="42.55" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="69" customWidth="1" min="4" max="4"/>
+    <col width="69" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -510,141 +576,384 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>3. AUDIT ZERO REDUNDANCY (ELIMINASI POTENSI TUMPANG TINDIH)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
           <t>Pasangan MK Berdekatan</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Titik Kritis Redundansi (Jika Tak Dibatasi)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Batasan Demarkasi Definitif (Buku Kurikulum 2026)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Bukti Dokumen (*Evidence*)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>**`STI-401 Machine Learning`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-501 Deep Learning`** (Sem 5)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Pengulangan materi regresi linier, decision tree, dan perceptron dasar.</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>**`STI-401`** fokus pada **Tabular &amp; Classical ML**: Scikit-Learn, Feature Engineering, SVM, Random Forest, K-Means, XGBoost.&lt;br&gt;**`STI-501`** fokus murni pada **Deep Representations &amp; Unstructured Data**: PyTorch/TensorFlow, Backpropagation, CNN (Vision), RNN/LSTM (Sequential), Attention Mechanism/Transformer.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>`007` Bagian 24 &amp; 32</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>**`STI-402 Data Warehouse &amp; BI`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-503 Data Mining &amp; Visualisasi`** (Sem 5)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Tumpang tindih pembersihan data (*data cleaning*) dan pembuatan grafik/dashboard.</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>**`STI-402`** berfokus pada **Arsitektur Data Enterprise**: Star Schema, Snowflake, ETL Pipeline, OLAP Cube, SSAS, Dashboard Eksekutif PowerBI/Tableau.&lt;br&gt;**`STI-503`** berfokus pada **Eksplorasi Pola Tersembunyi**: Algoritma Apriori/FP-Growth (Association Rules), Outlier Detection, Advanced Clustering, Dimensionality Reduction (PCA/t-SNE).</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>`007` Bagian 26 &amp; 34</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>**`STI-306 Web Front End`** (Sem 3)&lt;br&gt;vs&lt;br&gt;**`STI-407 Web Back End`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-604 Digital Platform Eng.`** (Sem 6)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Pengulangan pembuatan website monolitik sederhana (*CRUD Web*).</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>**`STI-306`** (Client-Side): HTML5, CSS Modern, JavaScript ES6+, React/Vue, DOM Manipulation, Responsive UI.&lt;br&gt;**`STI-407`** (Server-Side): RESTful API, NodeJS/Go/Python, JWT Authentication, ORM, Database Transactions, Redis Caching.&lt;br&gt;**`STI-604`** (Distributed Systems): Event-Driven Architecture, Message Broker (RabbitMQ/Kafka), API Gateway, Docker Containerization, CI/CD Pipeline.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>`007` Bagian 22, 29, 42</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>**`STI-405 Dasar Keamanan`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-603 Keamanan Lanjut`** (Sem 6)&lt;br&gt;vs&lt;br&gt;**`STB-01 Keamanan Jaringan`** (Sem 5)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Pengulangan konsep dasar CIA Triad dan antivirus/firewall.</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>**`STI-405`** (Teori Dasar): CIA Triad, Kriptografi Simetris/Asimetris Klasik (RSA/AES), Manajemen Risiko ISO 27001.&lt;br&gt;**`STB-01`** (Network Layer): Wireshark Packet Analysis, Snort IDS/IPS, VPN Tunnels, Digital Forensics Disk/Memory (Autopsy).&lt;br&gt;**`STI-603` / `STB-03`** (Application &amp; Offensive): OWASP Top 10, Penetration Testing (BurpSuite, Kali Linux), Reverse Engineering, Web Exploit Mitigation.</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>`007` Bagian 28, 41 &amp; `006` STB-01/03</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>**`STI-103 Arsitektur &amp; Org. STI`** (Sem 1)&lt;br&gt;vs&lt;br&gt;**`STI-201 Matdis &amp; Logika`** (Sem 2)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Pemisahan redundan antara Logika Proposisi dan Matematika Diskrit.</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Logika Informatika lama **dilebur penuh** ke dalam **`STI-201 Matematika Diskrit dan Logika (3 SKS)`**.&lt;br&gt;Slot Semester 1 dimanfaatkan untuk **`STI-103 Arsitektur dan Organisasi Sistem TI (3 SKS)`** sebagai fondasi hardware/cloud tanpa redundansi.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>`007` Bagian 5 &amp; 9</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>5. AUDIT FORENSIK PRASYARAT &amp; RESOLUSI KODE LATEN</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Dokumen &amp; Baris</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Nomenklatur Awal (Laten)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Nomenklatur Definitif (Tersinkronisasi)</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Justifikasi Pedagogis &amp; Logika Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>`005` : Baris 114</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>`STI-301 APSI` $\leftarrow$ `STI-104`</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>`STI-301 APSI` $\leftarrow$ **`STI-101`** Pengantar SI &amp; TI, `FST-207` Basis Data</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Memastikan fondasi analisis sistem merujuk pada Pengantar SI &amp; TI Sem 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>`005` : Baris 116</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>`STI-303 UI/UX` $\leftarrow$ `STI-104`</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>`STI-303 UI/UX` $\leftarrow$ **`FST-101`** Dasar Teknologi Digital</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>UI/UX berfondasi pada pemahaman interaksi teknologi digital modern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>`005` : Baris 120</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>`STI-307 Jarkom` $\leftarrow$ `STI-104`</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>`STI-307 Jarkom` $\leftarrow$ **`STI-103`** Arsitektur &amp; Organisasi Sistem TI</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Jaringan komputer memerlukan pemahaman datapath, bus biner, dan arsitektur hardware Sem 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>`007` : Baris 1520</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>`STI-505 Mobile` $\leftarrow$ `STI-205`</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>`STI-505 Mobile` $\leftarrow$ **`FST-203`** Struktur Data, `STI-306` Web Front-End</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Pemrograman Mobile membutuhkan pemahaman struktur data OOP dan state UI frontend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>`012` : Baris 251</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>`FST-611 Metpen` $\leftarrow$ `FST-208`</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>`FST-611 Metpen` $\leftarrow$ **`FST-408`** Probabilitas &amp; Statistika (Sem 4)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Menghilangkan rujukan usang `FST-208` dan menyelaraskan ke Probstat Sem 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>`012` : Baris 265</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>`STB-04 COBIT` $\leftarrow$ `STI-205`</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>`STB-04 COBIT` $\leftarrow$ **`FST-206`** Etika Profesi &amp; Hukum Digital (Sem 2)</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Tata kelola COBIT 2019 mensyaratkan etika profesi &amp; hukum siber Sem 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>`BUKU_FINAL` : 2738</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>`STI-505 Mobile` $\leftarrow$ `STI-205`</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>`STI-505 Mobile` $\leftarrow$ **`FST-203`** Struktur Data, `STI-306` Web Front-End</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Sinkronisasi penuh silabus lampiran Bab 7.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
+++ b/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
@@ -613,7 +613,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>**`STI-401 Machine Learning`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-501 Deep Learning`** (Sem 5)</t>
+          <t>**`STI-413 Machine Learning`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-626 Deep Learning`** (Sem 5)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>**`STI-401`** fokus pada **Tabular &amp; Classical ML**: Scikit-Learn, Feature Engineering, SVM, Random Forest, K-Means, XGBoost.&lt;br&gt;**`STI-501`** fokus murni pada **Deep Representations &amp; Unstructured Data**: PyTorch/TensorFlow, Backpropagation, CNN (Vision), RNN/LSTM (Sequential), Attention Mechanism/Transformer.</t>
+          <t>**`STI-413`** fokus pada **Tabular &amp; Classical ML**: Scikit-Learn, Feature Engineering, SVM, Random Forest, K-Means, XGBoost.&lt;br&gt;**`STI-519`** fokus murni pada **Deep Representations &amp; Unstructured Data**: PyTorch/TensorFlow, Backpropagation, CNN (Vision), RNN/LSTM (Sequential), Attention Mechanism/Transformer.</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>**`STI-402 Data Warehouse &amp; BI`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-503 Data Mining &amp; Visualisasi`** (Sem 5)</t>
+          <t>**`STI-415 Data Warehouse &amp; BI`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-520 Data Mining &amp; Visualisasi`** (Sem 5)</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>**`STI-402`** berfokus pada **Arsitektur Data Enterprise**: Star Schema, Snowflake, ETL Pipeline, OLAP Cube, SSAS, Dashboard Eksekutif PowerBI/Tableau.&lt;br&gt;**`STI-503`** berfokus pada **Eksplorasi Pola Tersembunyi**: Algoritma Apriori/FP-Growth (Association Rules), Outlier Detection, Advanced Clustering, Dimensionality Reduction (PCA/t-SNE).</t>
+          <t>**`STI-415`** berfokus pada **Arsitektur Data Enterprise**: Star Schema, Snowflake, ETL Pipeline, OLAP Cube, SSAS, Dashboard Eksekutif PowerBI/Tableau.&lt;br&gt;**`STI-520`** berfokus pada **Eksplorasi Pola Tersembunyi**: Algoritma Apriori/FP-Growth (Association Rules), Outlier Detection, Advanced Clustering, Dimensionality Reduction (PCA/t-SNE).</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>**`STI-306 Web Front End`** (Sem 3)&lt;br&gt;vs&lt;br&gt;**`STI-407 Web Back End`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-604 Digital Platform Eng.`** (Sem 6)</t>
+          <t>**`STI-311 Web Front End`** (Sem 3)&lt;br&gt;vs&lt;br&gt;**`STI-416 Web Back End`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-627 Digital Platform Eng.`** (Sem 6)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>**`STI-306`** (Client-Side): HTML5, CSS Modern, JavaScript ES6+, React/Vue, DOM Manipulation, Responsive UI.&lt;br&gt;**`STI-407`** (Server-Side): RESTful API, NodeJS/Go/Python, JWT Authentication, ORM, Database Transactions, Redis Caching.&lt;br&gt;**`STI-604`** (Distributed Systems): Event-Driven Architecture, Message Broker (RabbitMQ/Kafka), API Gateway, Docker Containerization, CI/CD Pipeline.</t>
+          <t>**`STI-311`** (Client-Side): HTML5, CSS Modern, JavaScript ES6+, React/Vue, DOM Manipulation, Responsive UI.&lt;br&gt;**`STI-416`** (Server-Side): RESTful API, NodeJS/Go/Python, JWT Authentication, ORM, Database Transactions, Redis Caching.&lt;br&gt;**`STI-627`** (Distributed Systems): Event-Driven Architecture, Message Broker (RabbitMQ/Kafka), API Gateway, Docker Containerization, CI/CD Pipeline.</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>**`STI-405 Dasar Keamanan`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-603 Keamanan Lanjut`** (Sem 6)&lt;br&gt;vs&lt;br&gt;**`STB-01 Keamanan Jaringan`** (Sem 5)</t>
+          <t>**`STI-418 Dasar Keamanan`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-519 Keamanan Lanjut`** (Sem 6)&lt;br&gt;vs&lt;br&gt;**`STB-01 Keamanan Jaringan`** (Sem 5)</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>**`STI-405`** (Teori Dasar): CIA Triad, Kriptografi Simetris/Asimetris Klasik (RSA/AES), Manajemen Risiko ISO 27001.&lt;br&gt;**`STB-01`** (Network Layer): Wireshark Packet Analysis, Snort IDS/IPS, VPN Tunnels, Digital Forensics Disk/Memory (Autopsy).&lt;br&gt;**`STI-603` / `STB-03`** (Application &amp; Offensive): OWASP Top 10, Penetration Testing (BurpSuite, Kali Linux), Reverse Engineering, Web Exploit Mitigation.</t>
+          <t>**`STI-418`** (Teori Dasar): CIA Triad, Kriptografi Simetris/Asimetris Klasik (RSA/AES), Manajemen Risiko ISO 27001.&lt;br&gt;**`STB-01`** (Network Layer): Wireshark Packet Analysis, Snort IDS/IPS, VPN Tunnels, Digital Forensics Disk/Memory (Autopsy).&lt;br&gt;**`STI-626` / `STB-03`** (Application &amp; Offensive): OWASP Top 10, Penetration Testing (BurpSuite, Kali Linux), Reverse Engineering, Web Exploit Mitigation.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>**`STI-103 Arsitektur &amp; Org. STI`** (Sem 1)&lt;br&gt;vs&lt;br&gt;**`STI-201 Matdis &amp; Logika`** (Sem 2)</t>
+          <t>**`STI-103 Arsitektur &amp; Org. STI`** (Sem 1)&lt;br&gt;vs&lt;br&gt;**`STI-204 Matdis &amp; Logika`** (Sem 2)</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Logika Informatika lama **dilebur penuh** ke dalam **`STI-201 Matematika Diskrit dan Logika (3 SKS)`**.&lt;br&gt;Slot Semester 1 dimanfaatkan untuk **`STI-103 Arsitektur dan Organisasi Sistem TI (3 SKS)`** sebagai fondasi hardware/cloud tanpa redundansi.</t>
+          <t>Logika Informatika lama **dilebur penuh** ke dalam **`STI-204 Matematika Diskrit dan Logika (3 SKS)`**.&lt;br&gt;Slot Semester 1 dimanfaatkan untuk **`STI-103 Arsitektur dan Organisasi Sistem TI (3 SKS)`** sebagai fondasi hardware/cloud tanpa redundansi.</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>`STI-301 APSI` $\leftarrow$ `STI-104`</t>
+          <t>`STI-306 APSI` $\leftarrow$ `STI-104`</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>`STI-301 APSI` $\leftarrow$ **`STI-101`** Pengantar SI &amp; TI, `FST-207` Basis Data</t>
+          <t>`STI-306 APSI` $\leftarrow$ **`STI-101`** Pengantar SI &amp; TI, `FST-207` Basis Data</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>`STI-303 UI/UX` $\leftarrow$ `STI-104`</t>
+          <t>`STI-308 UI/UX` $\leftarrow$ `STI-104`</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>`STI-303 UI/UX` $\leftarrow$ **`FST-101`** Dasar Teknologi Digital</t>
+          <t>`STI-308 UI/UX` $\leftarrow$ **`FST-101`** Dasar Teknologi Digital</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>`STI-307 Jarkom` $\leftarrow$ `STI-104`</t>
+          <t>`STI-312 Jarkom` $\leftarrow$ `STI-104`</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>`STI-307 Jarkom` $\leftarrow$ **`STI-103`** Arsitektur &amp; Organisasi Sistem TI</t>
+          <t>`STI-312 Jarkom` $\leftarrow$ **`STI-103`** Arsitektur &amp; Organisasi Sistem TI</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>`STI-505 Mobile` $\leftarrow$ `STI-205`</t>
+          <t>`STI-522 Mobile` $\leftarrow$ `STI-205`</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>`STI-505 Mobile` $\leftarrow$ **`FST-203`** Struktur Data, `STI-306` Web Front-End</t>
+          <t>`STI-522 Mobile` $\leftarrow$ **`FST-203`** Struktur Data, `STI-311` Web Front-End</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>`STI-505 Mobile` $\leftarrow$ `STI-205`</t>
+          <t>`STI-522 Mobile` $\leftarrow$ `STI-205`</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>`STI-505 Mobile` $\leftarrow$ **`FST-203`** Struktur Data, `STI-306` Web Front-End</t>
+          <t>`STI-522 Mobile` $\leftarrow$ **`FST-203`** Struktur Data, `STI-311` Web Front-End</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">

--- a/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
+++ b/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
@@ -613,7 +613,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>**`STI-413 Machine Learning`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-626 Deep Learning`** (Sem 5)</t>
+          <t>**`STI-413 Machine Learning`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-626 Deep Learning`** (Sem 6)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>**`STI-413`** fokus pada **Tabular &amp; Classical ML**: Scikit-Learn, Feature Engineering, SVM, Random Forest, K-Means, XGBoost.&lt;br&gt;**`STI-519`** fokus murni pada **Deep Representations &amp; Unstructured Data**: PyTorch/TensorFlow, Backpropagation, CNN (Vision), RNN/LSTM (Sequential), Attention Mechanism/Transformer.</t>
+          <t>**`STI-413`** fokus pada **Tabular &amp; Classical ML**: Scikit-Learn, Feature Engineering, SVM, Random Forest, K-Means, XGBoost.&lt;br&gt;**`STI-626`** fokus murni pada **Deep Representations &amp; Unstructured Data**: PyTorch/TensorFlow, Backpropagation, CNN (Vision), RNN/LSTM (Sequential), Attention Mechanism/Transformer.</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>`007` Bagian 24 &amp; 32</t>
+          <t>`007` Bagian 24 &amp; 40</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>**`STI-418 Dasar Keamanan`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-519 Keamanan Lanjut`** (Sem 6)&lt;br&gt;vs&lt;br&gt;**`STB-01 Keamanan Jaringan`** (Sem 5)</t>
+          <t>**`STI-418 Dasar Keamanan`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-519 Keamanan Lanjut`** (Sem 5)&lt;br&gt;vs&lt;br&gt;**`STB-01 Keamanan Jaringan`** (Sem 5)</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>**`STI-418`** (Teori Dasar): CIA Triad, Kriptografi Simetris/Asimetris Klasik (RSA/AES), Manajemen Risiko ISO 27001.&lt;br&gt;**`STB-01`** (Network Layer): Wireshark Packet Analysis, Snort IDS/IPS, VPN Tunnels, Digital Forensics Disk/Memory (Autopsy).&lt;br&gt;**`STI-626` / `STB-03`** (Application &amp; Offensive): OWASP Top 10, Penetration Testing (BurpSuite, Kali Linux), Reverse Engineering, Web Exploit Mitigation.</t>
+          <t>**`STI-418`** (Teori Dasar): CIA Triad, Kriptografi Simetris/Asimetris Klasik (RSA/AES), Manajemen Risiko ISO 27001.&lt;br&gt;**`STB-01`** (Network Layer): Wireshark Packet Analysis, Snort IDS/IPS, VPN Tunnels, Digital Forensics Disk/Memory (Autopsy).&lt;br&gt;**`STI-519` / `STB-03`** (Application &amp; Offensive): OWASP Top 10, Penetration Testing (BurpSuite, Kali Linux), Reverse Engineering, Web Exploit Mitigation.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>`007` Bagian 28, 41 &amp; `006` STB-01/03</t>
+          <t>`007` Bagian 28, 32 &amp; `006` STB-01/03</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
+++ b/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
@@ -679,7 +679,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>**`STI-418 Dasar Keamanan`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-519 Keamanan Lanjut`** (Sem 5)&lt;br&gt;vs&lt;br&gt;**`STB-01 Keamanan Jaringan`** (Sem 5)</t>
+          <t>**`STI-418 Dasar Keamanan`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-519 Keamanan Lanjut`** (Sem 5)&lt;br&gt;vs&lt;br&gt;**`STB-501 Keamanan Jaringan`** (Sem 5)</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>**`STI-418`** (Teori Dasar): CIA Triad, Kriptografi Simetris/Asimetris Klasik (RSA/AES), Manajemen Risiko ISO 27001.&lt;br&gt;**`STB-01`** (Network Layer): Wireshark Packet Analysis, Snort IDS/IPS, VPN Tunnels, Digital Forensics Disk/Memory (Autopsy).&lt;br&gt;**`STI-519` / `STB-03`** (Application &amp; Offensive): OWASP Top 10, Penetration Testing (BurpSuite, Kali Linux), Reverse Engineering, Web Exploit Mitigation.</t>
+          <t>**`STI-418`** (Teori Dasar): CIA Triad, Kriptografi Simetris/Asimetris Klasik (RSA/AES), Manajemen Risiko ISO 27001.&lt;br&gt;**`STB-501`** (Network Layer): Wireshark Packet Analysis, Snort IDS/IPS, VPN Tunnels, Digital Forensics Disk/Memory (Autopsy).&lt;br&gt;**`STI-519` / `STB-602`** (Application &amp; Offensive): OWASP Top 10, Penetration Testing (BurpSuite, Kali Linux), Reverse Engineering, Web Exploit Mitigation.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>`007` Bagian 28, 32 &amp; `006` STB-01/03</t>
+          <t>`007` Bagian 28, 32 &amp; `006` STB-501/03</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>`STB-04 COBIT` $\leftarrow$ `STI-205`</t>
+          <t>`STB-701 COBIT` $\leftarrow$ `STI-205`</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>`STB-04 COBIT` $\leftarrow$ **`FST-206`** Etika Profesi &amp; Hukum Digital (Sem 2)</t>
+          <t>`STB-701 COBIT` $\leftarrow$ **`FST-206`** Etika Profesi &amp; Hukum Digital (Sem 2)</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
